--- a/WAR3修仙项目/配置表格/__beans__.xlsx
+++ b/WAR3修仙项目/配置表格/__beans__.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\War3\mortal-cultivation-war3\tools\Luban\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\War3\mortal-cultivation-war3\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53A529C-4ED1-44D1-B3CC-EC68CBEFD079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5157588F-383D-4E05-A1ED-795614299111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="103">
   <si>
     <t>##var</t>
   </si>
@@ -86,13 +99,335 @@
   </si>
   <si>
     <t>字段变体</t>
+  </si>
+  <si>
+    <t>DropItem</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>e</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物大类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物子类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物名称</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>main_class</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sub_class</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>lv</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物档次</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>prob</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物概率</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>num</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落物数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tips_prob</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统提示概率</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attr</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>key</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttrKey</t>
+  </si>
+  <si>
+    <t>属性值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnMonster</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>count</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttrModifier</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttrKey</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>InfluenceOp</t>
+  </si>
+  <si>
+    <t>op</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>修正计算方法</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecMaterial</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回收材料id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回收材料数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipUpgrade</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cost_materials</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>array,RecMaterial</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级所需材料数组</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_key</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级属性值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级属性名</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性名</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_min</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_max</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_weight</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机属性下限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机属性上限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性掉落权重</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipAttrDrop</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性键值对</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性修正</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>修正属性名</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物生成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料回收</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备升级</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备属性随机掉落</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AffixDrop</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>词条随机掉落</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>weight</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>词条id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落权重</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>success_rate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级成功率万分比</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>套装效果</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>suit_count</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>套装数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>attrs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>array,Attr</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性加成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>套装技能id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>套装加成展示</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>suit_tips</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipSuit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +453,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -164,11 +507,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
@@ -451,13 +797,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="4" width="20.6640625" customWidth="1"/>
     <col min="5" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.4140625" customWidth="1"/>
+    <col min="7" max="7" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="15" customWidth="1"/>
+    <col min="10" max="11" width="13.4140625" customWidth="1"/>
+    <col min="12" max="12" width="14.9140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.33203125" customWidth="1"/>
     <col min="14" max="14" width="12.58203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -490,15 +838,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -553,6 +901,423 @@
       </c>
       <c r="P3" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" t="s">
+        <v>47</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="2"/>
+      <c r="J21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="2"/>
+      <c r="J23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="10:14" x14ac:dyDescent="0.3">
+      <c r="J33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
